--- a/05-halcyon-ai-governance/artifacts/ai_risk_assessment.xlsx
+++ b/05-halcyon-ai-governance/artifacts/ai_risk_assessment.xlsx
@@ -14,7 +14,7 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'AI Risk Register'!$A$1:$U$16</definedName>
-    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Method!$A$1:$B$9</definedName>
+    <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Area" vbProcedure="false">Method!$A$1:$B$12</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Area" vbProcedure="false">'Trustworthiness Coverage'!$A$1:$D$11</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -27,12 +27,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="168">
   <si>
     <t xml:space="preserve">HALCYON BENEFITS GROUP — AI RISK ASSESSMENT (NIST AI RMF MAP / MEASURE)</t>
   </si>
   <si>
-    <t xml:space="preserve">Sample GRC portfolio artifact | Fictional company | Risks assessed against NIST AI RMF trustworthiness characteristics and AI 600-1 GenAI risk categories | Assessment date: 2026-07-22</t>
+    <t xml:space="preserve">Sample GRC portfolio artifact | Fictional company | Risks assessed against NIST AI RMF trustworthiness characteristics and AI 600-1 GenAI risk categories | EU AI Act as amended by Reg. (EU) 2026/1744 (in force 27 Jul 2026) | Assessment date: 2026-08-05</t>
   </si>
   <si>
     <t xml:space="preserve">Risk ID</t>
@@ -194,7 +194,7 @@
     <t xml:space="preserve">AIR-004</t>
   </si>
   <si>
-    <t xml:space="preserve">System operating for 3 EU-based client plans without conformity assessment, technical documentation, or EU database registration required for high-risk AI.</t>
+    <t xml:space="preserve">If ClaimSight is High-Risk under Annex III, it operates for 3 EU client plans without conformity assessment, technical documentation, or database registration. Classification is contested: Annex III(5)(a) covers public-authority benefits and (5)(c) covers insurance risk/pricing — neither cleanly covers private claims adjudication.</t>
   </si>
   <si>
     <t xml:space="preserve">Regulatory (EU AI Act); contractual</t>
@@ -203,10 +203,10 @@
     <t xml:space="preserve">Halcyon; EU clients</t>
   </si>
   <si>
-    <t xml:space="preserve">None specific to AI Act.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">See Decision Memo. Options: (a) build conformity path, (b) carve EU plans out to manual adjudication, (c) exit EU book. Recommendation in memo.</t>
+    <t xml:space="preserve">None specific to AI Act. Digital Omnibus (Reg. 2026/1744, in force 27 Jul 2026) moved the Annex III deadline to 2 Dec 2027, creating runway that did not exist a month ago.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Obtain written counsel determination on Annex III applicability by 30 Sep 2026 — this is the gating question. Proceed with fairness and explainability work regardless, since it is required on its merits. See Decision Memo for both classification outcomes.</t>
   </si>
   <si>
     <t xml:space="preserve">Govern</t>
@@ -215,7 +215,7 @@
     <t xml:space="preserve">General Counsel + VP Claims</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-31 (decision)</t>
+    <t xml:space="preserve">2026-09-30 (counsel determination)</t>
   </si>
   <si>
     <t xml:space="preserve">AIR-005</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">Human-AI Configuration</t>
   </si>
   <si>
-    <t xml:space="preserve">Members not clearly informed they are interacting with AI; some believe they are chatting with a licensed representative.</t>
+    <t xml:space="preserve">Members not clearly informed they are interacting with AI. Art. 50 transparency duties were expressly NOT deferred by the Digital Omnibus and applied from 2 Aug 2026 — this obligation is live now, unlike the Annex III high-risk duties.</t>
   </si>
   <si>
     <t xml:space="preserve">Regulatory (AI Act Art. 50 transparency); trust</t>
@@ -287,90 +287,93 @@
     <t xml:space="preserve">Small footer text.</t>
   </si>
   <si>
-    <t xml:space="preserve">Prominent disclosure at session start; persistent AI indicator; easy path to human. Low effort, closes a legal obligation.</t>
+    <t xml:space="preserve">Prominent disclosure at session start; persistent AI indicator; easy path to human. Lowest effort item in the register and the only one already past its legal deadline. Do this first.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-15 (overdue)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIR-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Secure &amp; Resilient</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Information Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prompt injection via member-submitted text could extract system prompt or induce off-policy responses; RAG index includes documents with internal notes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data exposure; abuse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Halcyon; members</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure content filters (default).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Red-team with OWASP LLM Top 10 test cases; scrub RAG index to member-facing documents only; input/output filtering; log and alert on injection signatures.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIR-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI-007 M365 Copilot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Privacy-Enhanced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Privacy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copilot indexes SharePoint libraries containing PHI; users can surface member records they lack a need to know via natural-language query.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Privacy breach (HIPAA); regulatory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Members; Halcyon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SharePoint permissions (over-broad in legacy sites).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restrict Copilot semantic index from PHI-classified sites; sensitivity labels + DLP for AI-generated content; access recertification on legacy libraries first.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIR-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI-009 Shadow AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staff pasting member data into consumer AI tools; no contractual protection, potential training-data ingestion.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Privacy breach; regulatory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Members</t>
+  </si>
+  <si>
+    <t xml:space="preserve">None.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI acceptable use policy; CASB block on consumer AI endpoints; sanctioned enterprise alternative (AI-007) with data protections; awareness campaign; monitor CASB for residual usage.</t>
   </si>
   <si>
     <t xml:space="preserve">2026-08-31</t>
   </si>
   <si>
-    <t xml:space="preserve">AIR-008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Secure &amp; Resilient</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Information Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prompt injection via member-submitted text could extract system prompt or induce off-policy responses; RAG index includes documents with internal notes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data exposure; abuse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Halcyon; members</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure content filters (default).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Red-team with OWASP LLM Top 10 test cases; scrub RAG index to member-facing documents only; input/output filtering; log and alert on injection signatures.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CISO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIR-009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI-007 M365 Copilot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Privacy-Enhanced</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Privacy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Copilot indexes SharePoint libraries containing PHI; users can surface member records they lack a need to know via natural-language query.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Privacy breach (HIPAA); regulatory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Members; Halcyon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SharePoint permissions (over-broad in legacy sites).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restrict Copilot semantic index from PHI-classified sites; sensitivity labels + DLP for AI-generated content; access recertification on legacy libraries first.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIR-010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI-009 Shadow AI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Staff pasting member data into consumer AI tools; no contractual protection, potential training-data ingestion.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Privacy breach; regulatory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Members</t>
-  </si>
-  <si>
-    <t xml:space="preserve">None.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI acceptable use policy; CASB block on consumer AI endpoints; sanctioned enterprise alternative (AI-007) with data protections; awareness campaign; monitor CASB for residual usage.</t>
-  </si>
-  <si>
     <t xml:space="preserve">AIR-011</t>
   </si>
   <si>
@@ -504,6 +507,24 @@
   </si>
   <si>
     <t xml:space="preserve">AIR-004 and AIR-005 are the two risks that cannot be treated by controls alone — they require a business decision about whether to continue the use case. Those decisions are documented in the accompanying memo, not here.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regulatory status as assessed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Digital Omnibus on AI (Regulation (EU) 2026/1744) was published in the Official Journal on 24 July 2026 and entered into force on 27 July 2026. It defers Annex III standalone high-risk obligations from 2 August 2026 to 2 December 2027, and Annex I embedded high-risk systems to 2 August 2028. It does NOT defer Article 50 transparency duties, the Article 5 prohibitions, or GPAI provider obligations. The deferral is therefore selective, and treating it as a blanket extension is the error to avoid.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Why the deferral does not reduce urgency here</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two reasons. First, the one obligation that is live now — Art. 50 transparency, AIR-007 — is the one we had not met. Second, AIR-001 (encoded bias in denial recommendations) has no compliance date attached to it. The model either discriminates or it does not, and we currently cannot say which. Deadlines govern enforcement, not harm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contested classification</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIR-004 turns on whether ClaimSight falls within Annex III. It is not clearly enumerated: (5)(a) addresses essential public assistance benefits administered by public authorities, and (5)(c) addresses risk assessment and pricing for life and health insurance. A private administrator adjudicating employer-sponsored benefit claims sits between them. The register treats it as high-risk pending counsel determination, which is the conservative posture, and the Decision Memo presents both outcomes.</t>
   </si>
   <si>
     <t xml:space="preserve">Not legal advice</t>
@@ -1334,7 +1355,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
         <v>54</v>
       </c>
@@ -1541,7 +1562,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
         <v>81</v>
       </c>
@@ -1814,30 +1835,30 @@
         <v>96</v>
       </c>
       <c r="U14" s="4" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>26</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H15" s="4" t="n">
         <v>3</v>
@@ -1854,7 +1875,7 @@
         <v>Medium</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M15" s="4" t="n">
         <v>2</v>
@@ -1871,27 +1892,27 @@
         <v>Medium</v>
       </c>
       <c r="Q15" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="R15" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="S15" s="4" t="s">
         <v>33</v>
       </c>
       <c r="T15" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="U15" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>37</v>
@@ -1900,13 +1921,13 @@
         <v>26</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H16" s="4" t="n">
         <v>5</v>
@@ -1943,16 +1964,16 @@
         <v>31</v>
       </c>
       <c r="R16" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="S16" s="4" t="s">
         <v>60</v>
       </c>
       <c r="T16" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="U16" s="4" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -2020,26 +2041,26 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2055,12 +2076,12 @@
         <v>Medium</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B6" s="4" t="n">
         <f aca="false">COUNTIF('AI Risk Register'!$C$5:$C$16,A6)</f>
@@ -2071,7 +2092,7 @@
         <v>—</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2087,7 +2108,7 @@
         <v>Medium</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2103,12 +2124,12 @@
         <v>Critical</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B9" s="4" t="n">
         <f aca="false">COUNTIF('AI Risk Register'!$C$5:$C$16,A9)</f>
@@ -2119,7 +2140,7 @@
         <v>Medium</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2135,7 +2156,7 @@
         <v>Medium</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2151,7 +2172,7 @@
         <v>Critical</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -2184,7 +2205,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -2193,63 +2214,87 @@
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>167</v>
       </c>
     </row>
   </sheetData>
